--- a/RobotOnTheFloor/RNN_Ts5/Odometry.xlsx
+++ b/RobotOnTheFloor/RNN_Ts5/Odometry.xlsx
@@ -491,22 +491,22 @@
         <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.090655132497305</v>
+        <v>0.3700892820783209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5178728038946311</v>
+        <v>0.06408087391560359</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.753098386349968</v>
+        <v>-0.7157309450243925</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3788730723804385</v>
+        <v>0.136762213125315</v>
       </c>
       <c r="I2" t="n">
-        <v>-18.48007785998037</v>
+        <v>-4.298552152493733</v>
       </c>
       <c r="J2" t="n">
-        <v>5.507491891555148</v>
+        <v>1.49802958831042</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.547112110686549</v>
+        <v>0.7967824116790907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2591179438132786</v>
+        <v>0.02067334351380949</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.054803834892581</v>
+        <v>-0.4714010726041251</v>
       </c>
       <c r="H3" t="n">
-        <v>0.163789969991069</v>
+        <v>0.1172864939388509</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.59676950305271</v>
+        <v>-2.429329489599783</v>
       </c>
       <c r="J3" t="n">
-        <v>3.278688846388482</v>
+        <v>0.969554870016356</v>
       </c>
     </row>
     <row r="4">
@@ -559,22 +559,22 @@
         <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.601370661578016</v>
+        <v>0.7553970952454969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2646376710692162</v>
+        <v>0.02488347547201538</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.390999538475937</v>
+        <v>-0.8822938281698189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3500098989621407</v>
+        <v>0.1500390666958367</v>
       </c>
       <c r="I4" t="n">
-        <v>-8.376729540448046</v>
+        <v>-1.719557680646527</v>
       </c>
       <c r="J4" t="n">
-        <v>2.651029543337528</v>
+        <v>0.7688851134187595</v>
       </c>
     </row>
     <row r="5">
@@ -593,22 +593,22 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8158060419528044</v>
+        <v>0.8506011159584762</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01873806789727604</v>
+        <v>0.01519836189322805</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.197865962190209</v>
+        <v>-1.334315788741802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2549043179150855</v>
+        <v>0.1860700795352009</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5699258799959364</v>
+        <v>0.3036604222073881</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4438562369498104</v>
+        <v>0.1968721380903973</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.01026832613585</v>
+        <v>-0.0938181764510071</v>
       </c>
       <c r="F6" t="n">
-        <v>1.310059486388435</v>
+        <v>0.1022797597509658</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.227185960776853</v>
+        <v>-36.83672597025333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.378697852966651</v>
+        <v>1.98260940924817</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.919547455098212</v>
+        <v>-1.57760998663233</v>
       </c>
       <c r="J6" t="n">
-        <v>14.56794808760828</v>
+        <v>7.632915185409225</v>
       </c>
     </row>
     <row r="7">
@@ -661,22 +661,22 @@
         <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9784260814110035</v>
+        <v>-4.972756616487426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1849968748446974</v>
+        <v>0.5584951182356654</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.101874848613946</v>
+        <v>-5.551415236508396</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4769298149857982</v>
+        <v>0.3432880926855311</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03178171740182956</v>
+        <v>-0.01191928690466559</v>
       </c>
       <c r="J7" t="n">
-        <v>3.055350646384423</v>
+        <v>2.996533273644874</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.015551590939911</v>
+        <v>-7.702359763028442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3754825626700842</v>
+        <v>0.8137323780054113</v>
       </c>
       <c r="G8" t="n">
-        <v>-30.2764079736924</v>
+        <v>-25.38164719667971</v>
       </c>
       <c r="H8" t="n">
-        <v>1.638854820178614</v>
+        <v>1.38237388733697</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.232902497100475</v>
+        <v>-0.5549081294179259</v>
       </c>
       <c r="J8" t="n">
-        <v>6.61215446326073</v>
+        <v>4.604452160916948</v>
       </c>
     </row>
     <row r="9">
@@ -729,22 +729,22 @@
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8741746429994619</v>
+        <v>-3.846406614262659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1752486257261633</v>
+        <v>0.4531734019730642</v>
       </c>
       <c r="G9" t="n">
-        <v>-57.09391969997339</v>
+        <v>-37.41239942812954</v>
       </c>
       <c r="H9" t="n">
-        <v>3.044067605316214</v>
+        <v>2.012774165446608</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.532697724335513</v>
+        <v>-1.189515787518273</v>
       </c>
       <c r="J9" t="n">
-        <v>10.46115674806602</v>
+        <v>6.483676114661685</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2695432575855723</v>
+        <v>0.8019333719106383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.10140666765727</v>
+        <v>0.01582086833878536</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.332421600646582</v>
+        <v>0.367135050474211</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1381911721920001</v>
+        <v>0.03749594378218567</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.263278866821681</v>
+        <v>0.2236253359140845</v>
       </c>
       <c r="J10" t="n">
-        <v>1.708527643832724</v>
+        <v>0.3111355407419125</v>
       </c>
     </row>
     <row r="11">
@@ -797,22 +797,22 @@
         <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6825317767473531</v>
+        <v>0.2177380482026812</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02535824944504123</v>
+        <v>0.06248434410789754</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.086566325443167</v>
+        <v>0.3906069986801254</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1236247538993002</v>
+        <v>0.03610527923195769</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7663805727582624</v>
+        <v>0.5313267751531856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7078847366924544</v>
+        <v>0.1878228437756344</v>
       </c>
     </row>
     <row r="12">
@@ -831,22 +831,22 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2160677102521368</v>
+        <v>0.9243387281665636</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06261776485147134</v>
+        <v>0.006043557319922582</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.116295485667094</v>
+        <v>0.5906631400263909</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1846340841388165</v>
+        <v>0.02425236521796253</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.072501578306068</v>
+        <v>0.5172677263873293</v>
       </c>
       <c r="J12" t="n">
-        <v>1.231318439689383</v>
+        <v>0.1934570690310808</v>
       </c>
     </row>
     <row r="13">
@@ -865,22 +865,22 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4753129996448439</v>
+        <v>0.6881241219235719</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04191015938306371</v>
+        <v>0.02491155250476676</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.719124678509782</v>
+        <v>0.6746983759499217</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2795984100227331</v>
+        <v>0.01927345070504397</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.896268348687975</v>
+        <v>0.4675101008274349</v>
       </c>
       <c r="J13" t="n">
-        <v>1.56144657421546</v>
+        <v>0.2133976550016943</v>
       </c>
     </row>
     <row r="14">
@@ -899,22 +899,22 @@
         <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.198815204219736</v>
+        <v>-0.3510339290732423</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7638587695903424</v>
+        <v>0.1258717374439111</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.94625863810882</v>
+        <v>-0.1595278122076187</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4399109550505382</v>
+        <v>0.08578318205111679</v>
       </c>
       <c r="I14" t="n">
-        <v>-22.23502808371543</v>
+        <v>-4.623345513681829</v>
       </c>
       <c r="J14" t="n">
-        <v>7.736503176452339</v>
+        <v>1.872389836248123</v>
       </c>
     </row>
     <row r="15">
@@ -933,22 +933,22 @@
         <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.28848533304673</v>
+        <v>0.5765446094498877</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6790460938566998</v>
+        <v>0.03945205563793283</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4201664016858448</v>
+        <v>-0.2099975943619841</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1050655203748426</v>
+        <v>0.08951699375019566</v>
       </c>
       <c r="I15" t="n">
-        <v>-13.94717037133305</v>
+        <v>-2.750355580754132</v>
       </c>
       <c r="J15" t="n">
-        <v>4.976918066986945</v>
+        <v>1.248745547403292</v>
       </c>
     </row>
     <row r="16">
@@ -967,22 +967,22 @@
         <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.707367062352864</v>
+        <v>-0.03770712729629255</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7180720353350465</v>
+        <v>0.09668002872460288</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.826175876169916</v>
+        <v>-0.1036563315178556</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3570459625353622</v>
+        <v>0.08164974657072899</v>
       </c>
       <c r="I16" t="n">
-        <v>-18.92043958874461</v>
+        <v>-3.822140375055564</v>
       </c>
       <c r="J16" t="n">
-        <v>6.63285379296196</v>
+        <v>1.605614772424708</v>
       </c>
     </row>
     <row r="17">
@@ -1001,22 +1001,22 @@
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.789152271625677</v>
+        <v>-0.5768019625529148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7256917154680572</v>
+        <v>0.1469058610301892</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.911214896485188</v>
+        <v>-0.2634392461378101</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5852806466268535</v>
+        <v>0.09347066773294373</v>
       </c>
       <c r="I17" t="n">
-        <v>-21.28660440932074</v>
+        <v>-4.236106972832153</v>
       </c>
       <c r="J17" t="n">
-        <v>7.420709163071322</v>
+        <v>1.743452088011529</v>
       </c>
     </row>
   </sheetData>
